--- a/src/utils/sxsyzlzq/shijiesai/all8_count.xlsx
+++ b/src/utils/sxsyzlzq/shijiesai/all8_count.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\utils\sxsyzlzq\shijiesai\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
   <si>
     <t>区服+名字</t>
   </si>
@@ -58,49 +63,73 @@
     <t>总数</t>
   </si>
   <si>
+    <t>170-阿源</t>
+  </si>
+  <si>
     <t>166-阿白</t>
   </si>
   <si>
-    <t>170-阿源</t>
+    <t>149-灰企鹅呆瓜</t>
   </si>
   <si>
     <t>129-旧城之下</t>
   </si>
   <si>
+    <t>159-Jason</t>
+  </si>
+  <si>
     <t>157-段</t>
   </si>
   <si>
+    <t>144-zwy</t>
+  </si>
+  <si>
+    <t>166-顾圆（水貂兔</t>
+  </si>
+  <si>
+    <t>190-神秘人物</t>
+  </si>
+  <si>
+    <t>191-理解力</t>
+  </si>
+  <si>
     <t>151-星空</t>
   </si>
   <si>
-    <t>166-顾圆（水貂兔</t>
-  </si>
-  <si>
-    <t>190-神秘人物</t>
-  </si>
-  <si>
-    <t>191-理解力</t>
+    <t>148-大核桃</t>
+  </si>
+  <si>
+    <t>157-#</t>
   </si>
   <si>
     <t>133-叶小怪</t>
   </si>
   <si>
+    <t>165-龟龟强啊</t>
+  </si>
+  <si>
+    <t>167-qq</t>
+  </si>
+  <si>
+    <t>177-SHEN</t>
+  </si>
+  <si>
     <t>134-木轩</t>
   </si>
   <si>
     <t>145-小黑</t>
   </si>
   <si>
-    <t>149-灰企鹅呆瓜</t>
+    <t>146-KB</t>
   </si>
   <si>
     <t>151-suola</t>
   </si>
   <si>
-    <t>165-龟龟强啊</t>
-  </si>
-  <si>
-    <t>167-qq</t>
+    <t>166-mr</t>
+  </si>
+  <si>
+    <t>177-L</t>
   </si>
   <si>
     <t>186-豆、芽</t>
@@ -109,12 +138,27 @@
     <t>131-朝闻道</t>
   </si>
   <si>
+    <t>145-杜佳捷</t>
+  </si>
+  <si>
+    <t>148-淘汰郎</t>
+  </si>
+  <si>
+    <t>184-吾魂因土</t>
+  </si>
+  <si>
+    <t>130-随￥缘</t>
+  </si>
+  <si>
     <t>132-长腿欧胖</t>
   </si>
   <si>
     <t>133-海岸与风</t>
   </si>
   <si>
+    <t>133-神经蛙</t>
+  </si>
+  <si>
     <t>133-抹小布</t>
   </si>
   <si>
@@ -127,31 +171,37 @@
     <t>145-SZH</t>
   </si>
   <si>
-    <t>145-杜佳捷</t>
-  </si>
-  <si>
     <t>145-明</t>
   </si>
   <si>
     <t>148-12345</t>
   </si>
   <si>
-    <t>148-淘汰郎</t>
+    <t>148-请叫我阿奎</t>
   </si>
   <si>
     <t>150-开飞机的贝塔</t>
   </si>
   <si>
+    <t>161-淼</t>
+  </si>
+  <si>
     <t>161-青辰</t>
   </si>
   <si>
-    <t>177-SHEN</t>
+    <t>176-柳暗花明</t>
+  </si>
+  <si>
+    <t>177-一只废废猪</t>
   </si>
   <si>
     <t>178-lelev8</t>
   </si>
   <si>
-    <t>184-吾魂因土</t>
+    <t>182-shao</t>
+  </si>
+  <si>
+    <t>190-知足常乐</t>
   </si>
   <si>
     <t>总数：</t>
@@ -170,6 +220,18 @@
   </si>
   <si>
     <t>段</t>
+  </si>
+  <si>
+    <t>第十二届</t>
+  </si>
+  <si>
+    <t>企鹅</t>
+  </si>
+  <si>
+    <t>Jason</t>
+  </si>
+  <si>
+    <t>zwy</t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1154,52 +1216,64 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="I2">
         <f>SUM(B2:H2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="I3">
         <f>SUM(B3:H3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="D4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
       <c r="I4">
         <f>SUM(B4:H4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="E5">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
       <c r="I5">
         <f>SUM(B5:H5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="F6">
+      <c r="D6">
         <v>1</v>
       </c>
       <c r="I6">
@@ -1211,19 +1285,22 @@
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="F7">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
       <c r="I7">
         <f>SUM(B7:H7)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="F8">
+      <c r="E8">
         <v>1</v>
       </c>
       <c r="I8">
@@ -1238,52 +1315,64 @@
       <c r="F9">
         <v>1</v>
       </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
       <c r="I9">
         <f>SUM(B9:H9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>17</v>
       </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="I10">
         <f>SUM(B10:H10)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>18</v>
       </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="I11">
         <f>SUM(B11:H11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="G12">
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
         <f>SUM(B12:H12)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="G13">
+      <c r="F13">
         <v>1</v>
       </c>
       <c r="I13">
@@ -1295,7 +1384,7 @@
       <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="G14">
+      <c r="F14">
         <v>1</v>
       </c>
       <c r="I14">
@@ -1310,9 +1399,12 @@
       <c r="G15">
         <v>1</v>
       </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
       <c r="I15">
         <f>SUM(B15:H15)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1322,9 +1414,12 @@
       <c r="G16">
         <v>1</v>
       </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
       <c r="I16">
         <f>SUM(B16:H16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1334,28 +1429,34 @@
       <c r="G17">
         <v>1</v>
       </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
       <c r="I17">
         <f>SUM(B17:H17)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>25</v>
       </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18">
         <f>SUM(B18:H18)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="H19">
+      <c r="G19">
         <v>1</v>
       </c>
       <c r="I19">
@@ -1367,7 +1468,7 @@
       <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="H20">
+      <c r="G20">
         <v>1</v>
       </c>
       <c r="I20">
@@ -1379,7 +1480,7 @@
       <c r="A21" t="s">
         <v>28</v>
       </c>
-      <c r="H21">
+      <c r="G21">
         <v>1</v>
       </c>
       <c r="I21">
@@ -1391,7 +1492,7 @@
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="H22">
+      <c r="G22">
         <v>1</v>
       </c>
       <c r="I22">
@@ -1403,7 +1504,7 @@
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="H23">
+      <c r="G23">
         <v>1</v>
       </c>
       <c r="I23">
@@ -1415,7 +1516,7 @@
       <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="H24">
+      <c r="G24">
         <v>1</v>
       </c>
       <c r="I24">
@@ -1427,7 +1528,7 @@
       <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="H25">
+      <c r="G25">
         <v>1</v>
       </c>
       <c r="I25">
@@ -1440,11 +1541,11 @@
         <v>33</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26">
         <f>SUM(B26:H26)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1452,11 +1553,11 @@
         <v>34</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <f>SUM(B27:H27)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1464,11 +1565,11 @@
         <v>35</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <f>SUM(B28:H28)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1476,11 +1577,11 @@
         <v>36</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <f>SUM(B29:H29)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1531,77 +1632,274 @@
         <v>1</v>
       </c>
     </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <f>SUM(B34:H34)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <f>SUM(B35:H35)</f>
+        <v>1</v>
+      </c>
+    </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36">
-        <f t="shared" ref="B36:I36" si="0">SUM(B2:B33)</f>
-        <v>1</v>
-      </c>
-      <c r="C36">
+        <v>43</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <f>SUM(B36:H36)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <f>SUM(B37:H37)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <f>SUM(B38:H38)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <f>SUM(B39:H39)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <f>SUM(B40:H40)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <f>SUM(B41:H41)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <f>SUM(B42:H42)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <f>SUM(B43:H43)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <f>SUM(B44:H44)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <f>SUM(B45:H45)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <f>SUM(B46:H46)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <f>SUM(B47:H47)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <f>SUM(B48:H48)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51">
+        <f t="shared" ref="B51:I51" si="0">SUM(B2:B48)</f>
+        <v>2</v>
+      </c>
+      <c r="C51">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="D51">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="E51">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G36">
+        <v>2</v>
+      </c>
+      <c r="F51">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="H36">
+      <c r="G51">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="I36">
+      <c r="H51">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="B39" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="I51">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="B54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" t="s">
-        <v>46</v>
+    <row r="55" spans="1:9">
+      <c r="A55" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:9">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" t="s">
+        <v>59</v>
+      </c>
+      <c r="C56" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:I33">
-    <sortCondition ref="B2" descending="1"/>
+  <sortState ref="A2:I48">
+    <sortCondition ref="B3" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
